--- a/arista_territory2_chart.xlsx
+++ b/arista_territory2_chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/tarista_my_yearupunited_org/Documents/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{FD69E293-91CD-4DDF-9701-8A7B9533A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{211C36E4-FED6-4965-BBEB-101EE0AEA28E}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{FD69E293-91CD-4DDF-9701-8A7B9533A384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ED725B2-83D4-4928-91D7-85BC96F2D290}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{CF5DD148-3F6F-4AC3-8ACB-DBEE5A43C6DD}"/>
+    <workbookView minimized="1" xWindow="1740" yWindow="3120" windowWidth="2388" windowHeight="564" activeTab="1" xr2:uid="{CF5DD148-3F6F-4AC3-8ACB-DBEE5A43C6DD}"/>
   </bookViews>
   <sheets>
     <sheet name="region_total_rev" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="135" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -580,30 +580,12 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -725,6 +707,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-9D7A-417E-A803-576CF01C3D1F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -740,6 +727,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-9D7A-417E-A803-576CF01C3D1F}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -2908,7 +2900,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0EEC697-796A-4942-82C1-9DFA0B9BAE97}" name="PivotTable57" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0EEC697-796A-4942-82C1-9DFA0B9BAE97}" name="PivotTable57" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="A3:C5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisCol" showAll="0">
@@ -2938,10 +2930,10 @@
     <dataField name="Sum of total_rev" fld="1" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
